--- a/Pinout.xlsx
+++ b/Pinout.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dcdf7eb514dfaeec/Projects/Microgravity-Press-Washing-Machine/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="11_F25DC773A252ABDACC10482A015D75DE5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FAF7F4D-AF9A-4391-8CB8-D9100CC6CF7E}"/>
+  <xr:revisionPtr revIDLastSave="165" documentId="11_F25DC773A252ABDACC10482A015D75DE5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F15C756A-FB0D-4EEF-8611-ED4BAEB8D291}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="17472" windowHeight="10992" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,101 +26,47 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="41">
-  <si>
-    <t>D32</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="56">
   <si>
     <t>Air/Vacuum Selector V/v</t>
   </si>
   <si>
-    <t>D33</t>
-  </si>
-  <si>
     <t>Wash Pump Reversal V/v #1</t>
   </si>
   <si>
-    <t>D25</t>
-  </si>
-  <si>
     <t>Wash Pump Reversal V/v #2</t>
   </si>
   <si>
-    <t>D26</t>
-  </si>
-  <si>
     <t>Wash Chamber V/v</t>
   </si>
   <si>
-    <t>D27</t>
-  </si>
-  <si>
     <t>Clean wtr In V/v</t>
   </si>
   <si>
-    <t>D14</t>
-  </si>
-  <si>
     <t>Soil wtr out V/v</t>
   </si>
   <si>
-    <t>D12</t>
-  </si>
-  <si>
-    <t>D13</t>
-  </si>
-  <si>
     <t>Compression Tk V/v</t>
   </si>
   <si>
-    <t>Compensation Tk V/v</t>
-  </si>
-  <si>
-    <t>D21</t>
-  </si>
-  <si>
     <t>Wash Pump</t>
   </si>
   <si>
-    <t>D22</t>
-  </si>
-  <si>
     <t>Vacuum Pump</t>
   </si>
   <si>
-    <t>D19</t>
-  </si>
-  <si>
     <t>Detergent Pump</t>
   </si>
   <si>
-    <t>D23</t>
-  </si>
-  <si>
     <t>V/V Adj Bus Relay</t>
   </si>
   <si>
-    <t>D35</t>
-  </si>
-  <si>
     <t>E-Stop detect</t>
   </si>
   <si>
-    <t>D34</t>
-  </si>
-  <si>
     <t>Sensor unused</t>
   </si>
   <si>
-    <t>VN</t>
-  </si>
-  <si>
-    <t>Press Transducers</t>
-  </si>
-  <si>
-    <t>VP</t>
-  </si>
-  <si>
     <t>I/O</t>
   </si>
   <si>
@@ -141,13 +88,112 @@
     <t>A</t>
   </si>
   <si>
-    <t>D/A/PWM</t>
-  </si>
-  <si>
     <t>Pin Assignment</t>
   </si>
   <si>
     <t>Use</t>
+  </si>
+  <si>
+    <t>Instruction Label</t>
+  </si>
+  <si>
+    <t>Reservoir Tk V/v</t>
+  </si>
+  <si>
+    <t>oVA</t>
+  </si>
+  <si>
+    <t>oVWC</t>
+  </si>
+  <si>
+    <t>oVRT</t>
+  </si>
+  <si>
+    <t>oPW</t>
+  </si>
+  <si>
+    <t>oPV</t>
+  </si>
+  <si>
+    <t>oPD</t>
+  </si>
+  <si>
+    <t>oVB</t>
+  </si>
+  <si>
+    <t>iES</t>
+  </si>
+  <si>
+    <t>iPT1</t>
+  </si>
+  <si>
+    <t>iPT2</t>
+  </si>
+  <si>
+    <t>oVCW</t>
+  </si>
+  <si>
+    <t>oVSW</t>
+  </si>
+  <si>
+    <t>oVCT</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>idT</t>
+  </si>
+  <si>
+    <t>Change in Time</t>
+  </si>
+  <si>
+    <t>Internally Found</t>
+  </si>
+  <si>
+    <t>D/A/PWM/internal</t>
+  </si>
+  <si>
+    <t>internal</t>
+  </si>
+  <si>
+    <t>iT</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>3-Way</t>
+  </si>
+  <si>
+    <t>2-Way</t>
+  </si>
+  <si>
+    <t>Normally Open, Unused in Wash Instructions, controlled by microcontroller</t>
+  </si>
+  <si>
+    <t>VN input only pin</t>
+  </si>
+  <si>
+    <t>VP input only pin</t>
+  </si>
+  <si>
+    <t>oVR1</t>
+  </si>
+  <si>
+    <t>oVR2</t>
+  </si>
+  <si>
+    <t>Wash Chamber Press Transducer</t>
+  </si>
+  <si>
+    <t>Tank Press Transducer</t>
+  </si>
+  <si>
+    <t>iTS</t>
+  </si>
+  <si>
+    <t>Start Time of Instruction Execution</t>
   </si>
 </sst>
 </file>
@@ -189,8 +235,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -206,6 +253,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -471,245 +522,389 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C3:F19"/>
+  <dimension ref="C3:H22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="7" max="7" width="23.62890625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="3:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="3:8" x14ac:dyDescent="0.55000000000000004">
       <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="3:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="3:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="3:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8">
+        <v>27</v>
+      </c>
+      <c r="F8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="3:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10">
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="3:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11">
+        <v>13</v>
+      </c>
+      <c r="F11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="3:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12">
+        <v>21</v>
+      </c>
+      <c r="F12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="3:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="C13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13">
+        <v>22</v>
+      </c>
+      <c r="F13" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="3:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14">
+        <v>19</v>
+      </c>
+      <c r="F14" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="3:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="C15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15">
+        <v>23</v>
+      </c>
+      <c r="F15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="3:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="C16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16">
+        <v>35</v>
+      </c>
+      <c r="F16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="3:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17">
+        <v>34</v>
+      </c>
+      <c r="F17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="3:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="C18" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18">
+        <v>39</v>
+      </c>
+      <c r="F18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="3:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="C19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19">
+        <v>36</v>
+      </c>
+      <c r="F19" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="3:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="3:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="C21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" t="s">
         <v>38</v>
       </c>
-      <c r="D3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="G21" t="s">
         <v>39</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H21" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="3:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="C4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>0</v>
-      </c>
-      <c r="F4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="3:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>2</v>
-      </c>
-      <c r="F5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="3:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="C6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="3:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="C7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="3:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="3:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="3:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="C10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="3:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="3:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="C12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" t="s">
+    <row r="22" spans="3:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="C22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="13" spans="3:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="C13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="3:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="C14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="3:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="C15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E15" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="3:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="C16" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" t="s">
-        <v>33</v>
-      </c>
-      <c r="E16" t="s">
-        <v>24</v>
-      </c>
-      <c r="F16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="C17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" t="s">
-        <v>35</v>
-      </c>
-      <c r="E17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F17" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="3:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="C18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="3:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="C19" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19" t="s">
-        <v>30</v>
-      </c>
-      <c r="F19" t="s">
-        <v>29</v>
+      <c r="E22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" t="s">
+        <v>54</v>
+      </c>
+      <c r="G22" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
